--- a/translations.xlsx
+++ b/translations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="888">
   <si>
     <t xml:space="preserve">msg_id</t>
   </si>
@@ -455,6 +455,249 @@
   </si>
   <si>
     <t xml:space="preserve">Revisione %(name)s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jinja:scripts/templates/version_index.html.j2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geologisches Datenmodell – Verfügbare Versionen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modèle de données géologiques – Versions disponibles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modello di dati geologici – Versioni disponibili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geological Data Model – Available Versions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page_heading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🗺️ 2D Datenmodell Geologie (GeoCover)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">🗺️ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Modèle de données géologique 2D (GeoCover)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">🗺️ Modello dati geologico 2D (GeoCover)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🗺️ 2D Geological Data Model (GeoCover)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page_subtitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verfügbare Versionen des schweizerischen 2D geologischen Datenmodells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versions disponibles du modèle 2D de données géologiques suisse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versioni disponibili del modello 2D di dati geologici svizzero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Available versions of the Swiss geological 2D data model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">badge_latest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEUESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERNIÈRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LATEST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">badge_draft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENTWURF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BROUILLON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOZZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRAFT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no_versions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keine Versionen verfügbar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aucune version disponible pour le moment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nessuna versione disponibile al momento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No versions available at the moment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no_files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keine Dateien für diese Version verfügbar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aucun fichier disponible pour cette version.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nessun file disponibile per questa versione.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No files available for this version.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lang_de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lang_fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Französisch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Français</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">French</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lang_it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italienisch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italiano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lang_en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Englisch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anglais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inglese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lang_root</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gemeinsame Dateien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fichiers communs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File comuni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">version_label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">footer_generated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatisch generiert am {date} UTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Généré automatiquement le {date} UTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generato automaticamente il {date} UTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatically generated on {date} UTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">footer_github</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quellcode auf GitHub ansehen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voir le code source sur GitHub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visualizza il codice sorgente su GitHub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">View source code on GitHub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patch_tooltip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deployment-Version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version de déploiement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versione di distribuzione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deployment version</t>
   </si>
   <si>
     <t xml:space="preserve">themes &gt; Rock_Bodies &gt; classes &gt; Unconsolidated_Deposits_PT &gt; description</t>
@@ -2802,15 +3045,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G325"/>
-  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="17.35" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G1048576"/>
+  <sheetFormatPr defaultColWidth="9.18359375" defaultRowHeight="17.35" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="50.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="79.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="41.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="56.24"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="6" style="1" width="9.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="43.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="66.6"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="8" style="1" width="9.17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3107,7 +3352,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -3600,7 +3845,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
         <v>141</v>
       </c>
@@ -3616,5022 +3861,5460 @@
       <c r="E36" s="3" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="99.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="G36" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="32.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
         <v>146</v>
       </c>
+      <c r="B37" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="C37" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="1" t="s">
         <v>148</v>
       </c>
+      <c r="D37" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="G37" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="32.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="B38" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>148</v>
+      <c r="C38" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>148</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="32.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>149</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>148</v>
+      <c r="A40" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>149</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>148</v>
+      <c r="A41" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>148</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="32.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>148</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="32.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>149</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>148</v>
+      <c r="A44" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
-        <v>171</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="1" t="s">
-        <v>148</v>
+        <v>184</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>149</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>148</v>
+      <c r="A46" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>149</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>148</v>
+      <c r="A47" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>149</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>148</v>
+      <c r="A48" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>149</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>148</v>
+      <c r="A49" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>148</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="32.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>148</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="32.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>149</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>148</v>
+      <c r="A52" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="99.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>193</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
       <c r="F53" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
+        <v>241</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F59" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>217</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
       <c r="F61" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
+        <v>226</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="F62" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>151</v>
+        <v>251</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>152</v>
+        <v>252</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>182</v>
+        <v>257</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>185</v>
+        <v>260</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>182</v>
+        <v>270</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>182</v>
+        <v>273</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>177</v>
+        <v>277</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>241</v>
+        <v>278</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>179</v>
+        <v>279</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>242</v>
+        <v>281</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>179</v>
+        <v>282</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>180</v>
+        <v>283</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>243</v>
+        <v>284</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>180</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
       <c r="F75" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>244</v>
+        <v>287</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>245</v>
+        <v>288</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>246</v>
+        <v>289</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>166</v>
+        <v>291</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>217</v>
+        <v>292</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>248</v>
+        <v>293</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>190</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
       <c r="F78" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>253</v>
+        <v>297</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>254</v>
+        <v>298</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>255</v>
+        <v>299</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>256</v>
+        <v>300</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>257</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>258</v>
+        <v>301</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>259</v>
+        <v>302</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>260</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>261</v>
+        <v>303</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>262</v>
+        <v>304</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>263</v>
+        <v>305</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>264</v>
+        <v>306</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>265</v>
+        <v>307</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>266</v>
+        <v>308</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>267</v>
+        <v>309</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>268</v>
+        <v>310</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>269</v>
+        <v>311</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>270</v>
+        <v>311</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>271</v>
+        <v>312</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>274</v>
+        <v>313</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>288</v>
+        <v>255</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="99.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
       <c r="F93" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>151</v>
+        <v>324</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>152</v>
+        <v>265</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
+        <v>325</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>327</v>
+      </c>
       <c r="F95" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>299</v>
+        <v>328</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>151</v>
+        <v>329</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>152</v>
+        <v>330</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="182.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
+        <v>331</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>333</v>
+      </c>
       <c r="F97" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>151</v>
+        <v>335</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>152</v>
+        <v>336</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>304</v>
+        <v>337</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
+        <v>340</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>342</v>
+      </c>
       <c r="F100" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>310</v>
+        <v>343</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>151</v>
+        <v>344</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>152</v>
+        <v>345</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
+        <v>346</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>348</v>
+      </c>
       <c r="F102" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>314</v>
+        <v>349</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>151</v>
+        <v>350</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>152</v>
+        <v>351</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>315</v>
+        <v>352</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>316</v>
+        <v>353</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>317</v>
+        <v>354</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>318</v>
+        <v>355</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>320</v>
+        <v>357</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>322</v>
+        <v>359</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>323</v>
+        <v>360</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>324</v>
+        <v>361</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>326</v>
+        <v>363</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>328</v>
+        <v>365</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>329</v>
+        <v>366</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="99.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>332</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
       <c r="F109" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>333</v>
+        <v>370</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
+        <v>226</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="F110" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>152</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
       <c r="F111" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
+        <v>374</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="F112" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="182.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>152</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
       <c r="F113" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
+        <v>378</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="F114" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>344</v>
+        <v>379</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>151</v>
+        <v>380</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>152</v>
+        <v>381</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>345</v>
+        <v>382</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>347</v>
+        <v>384</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
       <c r="F116" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>348</v>
+        <v>385</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>351</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
       <c r="F118" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
+        <v>226</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="F119" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>355</v>
+        <v>390</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>151</v>
+        <v>391</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>152</v>
+        <v>392</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="D121" s="3"/>
-      <c r="E121" s="3"/>
+        <v>393</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>395</v>
+      </c>
       <c r="F121" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>151</v>
+        <v>397</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>152</v>
+        <v>398</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>360</v>
+        <v>399</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>362</v>
+        <v>401</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="D124" s="3"/>
-      <c r="E124" s="3"/>
+        <v>402</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="F124" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>366</v>
+        <v>405</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>152</v>
+        <v>407</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>369</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
       <c r="F126" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="D127" s="3"/>
-      <c r="E127" s="3"/>
+        <v>411</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="F127" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>375</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
       <c r="F128" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>376</v>
+        <v>415</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>377</v>
+        <v>226</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>378</v>
+        <v>227</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>380</v>
+        <v>417</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>381</v>
+        <v>418</v>
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
       <c r="F130" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>382</v>
+        <v>419</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>383</v>
+        <v>420</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>385</v>
+        <v>422</v>
       </c>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
       <c r="F132" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>386</v>
+        <v>423</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>387</v>
+        <v>424</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>388</v>
+        <v>425</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>375</v>
+        <v>426</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>389</v>
+        <v>427</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>391</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
       <c r="F135" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>392</v>
+        <v>430</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="D136" s="3"/>
-      <c r="E136" s="3"/>
+        <v>226</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="F136" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>152</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
       <c r="F137" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>396</v>
+        <v>434</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>397</v>
+        <v>226</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>398</v>
+        <v>227</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>404</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
       <c r="F140" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>406</v>
+        <v>226</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>407</v>
+        <v>227</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>408</v>
+        <v>442</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>409</v>
+        <v>444</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>411</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
       <c r="F143" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>154</v>
+        <v>449</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>155</v>
+        <v>450</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>413</v>
+        <v>451</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>414</v>
+        <v>452</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>415</v>
+        <v>453</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>418</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
       <c r="F146" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>419</v>
+        <v>457</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>420</v>
+        <v>226</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>421</v>
+        <v>227</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>422</v>
+        <v>458</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>424</v>
+        <v>460</v>
       </c>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
       <c r="F148" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>425</v>
+        <v>461</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>426</v>
+        <v>462</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>427</v>
+        <v>463</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>429</v>
+        <v>464</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>430</v>
+        <v>465</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>431</v>
+        <v>466</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>432</v>
+        <v>467</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>434</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
       <c r="F152" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>435</v>
+        <v>470</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>436</v>
+        <v>226</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>437</v>
+        <v>227</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>438</v>
+        <v>471</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>441</v>
+        <v>474</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="D156" s="3"/>
-      <c r="E156" s="3"/>
+        <v>477</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>479</v>
+      </c>
       <c r="F156" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>447</v>
+        <v>480</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>151</v>
+        <v>481</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>152</v>
+        <v>482</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>448</v>
+        <v>483</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>439</v>
+        <v>481</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>369</v>
+        <v>484</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>449</v>
+        <v>485</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>442</v>
+        <v>481</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>443</v>
+        <v>486</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="D160" s="3"/>
-      <c r="E160" s="3"/>
+        <v>229</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>230</v>
+      </c>
       <c r="F160" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>453</v>
+        <v>488</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>151</v>
+        <v>489</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>152</v>
+        <v>490</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>454</v>
+        <v>491</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>455</v>
+        <v>492</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>456</v>
+        <v>493</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>457</v>
+        <v>494</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>458</v>
+        <v>495</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>434</v>
+        <v>496</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>437</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
       <c r="F164" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>461</v>
+        <v>226</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>462</v>
+        <v>227</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>369</v>
+        <v>503</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>464</v>
+        <v>504</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>442</v>
+        <v>505</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>443</v>
+        <v>506</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>465</v>
+        <v>507</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C168" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="D168" s="3"/>
-      <c r="E168" s="3"/>
+        <v>508</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>509</v>
+      </c>
       <c r="F168" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>468</v>
+        <v>510</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>151</v>
+        <v>511</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>152</v>
+        <v>512</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>469</v>
+        <v>513</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>470</v>
+        <v>514</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>375</v>
+        <v>515</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>471</v>
+        <v>516</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="C171" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="D171" s="3"/>
-      <c r="E171" s="3"/>
+        <v>517</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>518</v>
+      </c>
       <c r="F171" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>152</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="D172" s="3"/>
+      <c r="E172" s="3"/>
       <c r="F172" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>475</v>
+        <v>522</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>476</v>
+        <v>226</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>477</v>
+        <v>227</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>478</v>
+        <v>523</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>479</v>
+        <v>514</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>480</v>
+        <v>444</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>482</v>
+        <v>517</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>483</v>
+        <v>518</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="176" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>484</v>
+        <v>525</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>155</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="D176" s="3"/>
+      <c r="E176" s="3"/>
       <c r="F176" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>485</v>
+        <v>528</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>486</v>
+        <v>226</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>170</v>
+        <v>227</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="178" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="C178" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="D178" s="3"/>
-      <c r="E178" s="3"/>
+        <v>529</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>531</v>
+      </c>
       <c r="F178" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>490</v>
+        <v>532</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>151</v>
+        <v>533</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>152</v>
+        <v>509</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>491</v>
+        <v>534</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>154</v>
+        <v>511</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>493</v>
+        <v>535</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>494</v>
+        <v>536</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>495</v>
+        <v>537</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>496</v>
+        <v>538</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>498</v>
+        <v>444</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="183" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>499</v>
+        <v>539</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="C183" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="D183" s="3"/>
-      <c r="E183" s="3"/>
+        <v>517</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>518</v>
+      </c>
       <c r="F183" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="184" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>152</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="D184" s="3"/>
+      <c r="E184" s="3"/>
       <c r="F184" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>503</v>
+        <v>543</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>504</v>
+        <v>226</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>505</v>
+        <v>227</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="186" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C186" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="D186" s="3"/>
-      <c r="E186" s="3"/>
+        <v>545</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="F186" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="187" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>509</v>
+        <v>546</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>152</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D187" s="3"/>
+      <c r="E187" s="3"/>
       <c r="F187" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>510</v>
+        <v>549</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>511</v>
+        <v>226</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>440</v>
+        <v>227</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="189" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="C189" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="D189" s="3"/>
-      <c r="E189" s="3"/>
+        <v>550</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>552</v>
+      </c>
       <c r="F189" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>515</v>
+        <v>553</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>151</v>
+        <v>554</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>152</v>
+        <v>555</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>516</v>
+        <v>556</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>517</v>
+        <v>557</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>518</v>
+        <v>558</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>519</v>
+        <v>559</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>520</v>
+        <v>229</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>521</v>
+        <v>230</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>522</v>
+        <v>560</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>523</v>
+        <v>561</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>524</v>
+        <v>245</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="194" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="D194" s="3"/>
+      <c r="E194" s="3"/>
       <c r="F194" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="195" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="B195" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="C195" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="D195" s="3"/>
-      <c r="E195" s="3"/>
+        <v>565</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="F195" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>530</v>
+        <v>566</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>151</v>
+        <v>229</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>152</v>
+        <v>567</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>531</v>
+        <v>568</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>532</v>
+        <v>569</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>533</v>
+        <v>570</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>535</v>
+        <v>572</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>536</v>
+        <v>573</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="199" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>537</v>
+        <v>574</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>217</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="D199" s="3"/>
+      <c r="E199" s="3"/>
       <c r="F199" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>539</v>
+        <v>577</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>540</v>
+        <v>226</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>541</v>
+        <v>227</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="201" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="B201" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="C201" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="D201" s="3"/>
-      <c r="E201" s="3"/>
+        <v>578</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>580</v>
+      </c>
       <c r="F201" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="202" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>545</v>
+        <v>581</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>152</v>
-      </c>
+        <v>582</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D202" s="3"/>
+      <c r="E202" s="3"/>
       <c r="F202" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>546</v>
+        <v>584</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>547</v>
+        <v>226</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>548</v>
+        <v>227</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="204" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>549</v>
+        <v>585</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="C204" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="D204" s="3"/>
-      <c r="E204" s="3"/>
+        <v>586</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>515</v>
+      </c>
       <c r="F204" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="205" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>152</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="D205" s="3"/>
+      <c r="E205" s="3"/>
       <c r="F205" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>553</v>
+        <v>590</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>554</v>
+        <v>226</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="C207" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="D207" s="3"/>
-      <c r="E207" s="3"/>
+        <v>591</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>593</v>
+      </c>
       <c r="F207" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>558</v>
+        <v>594</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>151</v>
+        <v>595</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>152</v>
+        <v>596</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>559</v>
+        <v>597</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>560</v>
+        <v>598</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>561</v>
+        <v>599</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>562</v>
+        <v>600</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>563</v>
+        <v>601</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>564</v>
+        <v>245</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="211" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>443</v>
-      </c>
+        <v>602</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D211" s="3"/>
+      <c r="E211" s="3"/>
       <c r="F211" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="s">
-        <v>566</v>
+        <v>605</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>567</v>
+        <v>226</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>568</v>
+        <v>227</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="213" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="B213" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="C213" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="D213" s="3"/>
-      <c r="E213" s="3"/>
+        <v>606</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>608</v>
+      </c>
       <c r="F213" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
-        <v>572</v>
+        <v>609</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>151</v>
+        <v>610</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>152</v>
+        <v>611</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="s">
-        <v>573</v>
+        <v>612</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>560</v>
+        <v>613</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>561</v>
+        <v>292</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
-        <v>574</v>
+        <v>614</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>575</v>
+        <v>615</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>576</v>
+        <v>616</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>578</v>
-      </c>
+        <v>617</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="D217" s="3"/>
+      <c r="E217" s="3"/>
       <c r="F217" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="C218" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="D218" s="3"/>
-      <c r="E218" s="3"/>
+        <v>620</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="F218" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
-        <v>582</v>
+        <v>621</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>151</v>
+        <v>622</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>152</v>
+        <v>623</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="220" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="s">
-        <v>583</v>
+        <v>624</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>369</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="D220" s="3"/>
+      <c r="E220" s="3"/>
       <c r="F220" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
-        <v>584</v>
+        <v>627</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>442</v>
+        <v>226</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>443</v>
+        <v>227</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="s">
-        <v>585</v>
+        <v>628</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>586</v>
+        <v>629</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>587</v>
+        <v>230</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="223" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>590</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="D223" s="3"/>
+      <c r="E223" s="3"/>
       <c r="F223" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="224" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="D224" s="3"/>
-      <c r="E224" s="3"/>
+        <v>633</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="F224" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="s">
-        <v>594</v>
+        <v>634</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>151</v>
+        <v>635</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>152</v>
+        <v>636</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
-        <v>595</v>
+        <v>637</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>596</v>
+        <v>638</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>597</v>
+        <v>639</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
-        <v>598</v>
+        <v>640</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>575</v>
+        <v>517</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>576</v>
+        <v>518</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
-        <v>599</v>
+        <v>641</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>600</v>
+        <v>642</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>601</v>
+        <v>643</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="229" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="C229" s="1" t="s">
-        <v>604</v>
-      </c>
+        <v>644</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="D229" s="3"/>
+      <c r="E229" s="3"/>
       <c r="F229" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="s">
-        <v>605</v>
+        <v>647</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="s">
-        <v>606</v>
+        <v>648</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>607</v>
+        <v>635</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>608</v>
+        <v>636</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
-        <v>609</v>
+        <v>649</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>610</v>
+        <v>650</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>611</v>
+        <v>651</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
-        <v>612</v>
+        <v>652</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>613</v>
+        <v>642</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>614</v>
+        <v>653</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="234" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>617</v>
-      </c>
+        <v>654</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="D234" s="3"/>
+      <c r="E234" s="3"/>
       <c r="F234" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="235" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="B235" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="C235" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="D235" s="3"/>
-      <c r="E235" s="3"/>
+        <v>657</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="F235" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>621</v>
+        <v>658</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>151</v>
+        <v>638</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>152</v>
+        <v>444</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>622</v>
+        <v>659</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>607</v>
+        <v>517</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>608</v>
+        <v>518</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>610</v>
+        <v>661</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>611</v>
+        <v>662</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>624</v>
+        <v>663</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>613</v>
+        <v>664</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>614</v>
+        <v>665</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="240" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="s">
-        <v>625</v>
+        <v>666</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>626</v>
+        <v>667</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>627</v>
+        <v>668</v>
       </c>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
       <c r="F240" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="s">
-        <v>628</v>
+        <v>669</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>629</v>
+        <v>670</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>607</v>
+        <v>671</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>608</v>
+        <v>672</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>630</v>
+        <v>673</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>610</v>
+        <v>650</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>611</v>
+        <v>651</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
-        <v>631</v>
+        <v>674</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>613</v>
+        <v>675</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>614</v>
+        <v>676</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="245" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="B245" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="C245" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="D245" s="3"/>
-      <c r="E245" s="3"/>
+        <v>677</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>679</v>
+      </c>
       <c r="F245" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>635</v>
+        <v>680</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
-        <v>636</v>
+        <v>681</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>637</v>
+        <v>682</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>638</v>
+        <v>683</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>639</v>
+        <v>684</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>640</v>
+        <v>685</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>641</v>
+        <v>686</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
-        <v>642</v>
+        <v>687</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>643</v>
+        <v>688</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>644</v>
+        <v>689</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
-        <v>645</v>
+        <v>690</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>646</v>
+        <v>691</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>647</v>
+        <v>692</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="251" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
-        <v>648</v>
+        <v>693</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>649</v>
+        <v>694</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>650</v>
+        <v>695</v>
       </c>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
       <c r="F251" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="s">
-        <v>652</v>
+        <v>697</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>640</v>
+        <v>682</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>641</v>
+        <v>683</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="254" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="B254" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="C254" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="D254" s="3"/>
-      <c r="E254" s="3"/>
+        <v>698</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>686</v>
+      </c>
       <c r="F254" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>656</v>
+        <v>699</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>151</v>
+        <v>688</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>152</v>
+        <v>689</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="256" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>638</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="D256" s="3"/>
+      <c r="E256" s="3"/>
       <c r="F256" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>658</v>
+        <v>703</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>640</v>
+        <v>226</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>641</v>
+        <v>227</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>659</v>
+        <v>704</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>643</v>
+        <v>682</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>660</v>
+        <v>683</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
-        <v>661</v>
+        <v>705</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>646</v>
+        <v>685</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>662</v>
+        <v>686</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="260" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="B260" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="C260" s="3" t="s">
-        <v>665</v>
-      </c>
-      <c r="D260" s="3"/>
-      <c r="E260" s="3"/>
+        <v>706</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>689</v>
+      </c>
       <c r="F260" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="261" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="B261" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C261" s="1" t="s">
-        <v>152</v>
-      </c>
+        <v>707</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="D261" s="3"/>
+      <c r="E261" s="3"/>
       <c r="F261" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="1" t="s">
-        <v>667</v>
+        <v>710</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>668</v>
+        <v>226</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>669</v>
+        <v>227</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="263" customFormat="false" ht="132.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="s">
-        <v>670</v>
+        <v>711</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="C263" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="D263" s="3"/>
-      <c r="E263" s="3"/>
+        <v>712</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>713</v>
+      </c>
       <c r="F263" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>673</v>
+        <v>714</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>674</v>
+        <v>715</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>675</v>
+        <v>716</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
-        <v>676</v>
+        <v>717</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>677</v>
+        <v>718</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>678</v>
+        <v>719</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
-        <v>679</v>
+        <v>720</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>680</v>
+        <v>721</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>681</v>
+        <v>722</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="267" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="C267" s="1" t="s">
-        <v>660</v>
-      </c>
+        <v>723</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="D267" s="3"/>
+      <c r="E267" s="3"/>
       <c r="F267" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>684</v>
+        <v>726</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>685</v>
+        <v>226</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>686</v>
+        <v>227</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>687</v>
+        <v>727</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>688</v>
+        <v>715</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>689</v>
+        <v>716</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="270" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="B270" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="C270" s="1" t="s">
-        <v>691</v>
-      </c>
+        <v>728</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="D270" s="3"/>
+      <c r="E270" s="3"/>
       <c r="F270" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
-        <v>692</v>
+        <v>731</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>693</v>
+        <v>226</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>694</v>
+        <v>227</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="s">
-        <v>695</v>
+        <v>732</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>696</v>
+        <v>712</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>697</v>
+        <v>713</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="s">
-        <v>698</v>
+        <v>733</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>442</v>
+        <v>715</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>443</v>
+        <v>716</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
-        <v>699</v>
+        <v>734</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>700</v>
+        <v>718</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>701</v>
+        <v>735</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>702</v>
+        <v>736</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>703</v>
+        <v>721</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>704</v>
+        <v>737</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="276" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="B276" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="C276" s="1" t="s">
-        <v>707</v>
-      </c>
+        <v>738</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="D276" s="3"/>
+      <c r="E276" s="3"/>
       <c r="F276" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="277" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="B277" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="C277" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="D277" s="3"/>
-      <c r="E277" s="3"/>
+        <v>741</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="F277" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
-        <v>711</v>
+        <v>742</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>151</v>
+        <v>743</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>152</v>
+        <v>744</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="279" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="132.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="B279" s="3" t="s">
-        <v>713</v>
+        <v>745</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>746</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>714</v>
+        <v>747</v>
       </c>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
       <c r="F279" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>715</v>
+        <v>748</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>151</v>
+        <v>749</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>152</v>
+        <v>750</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>716</v>
+        <v>751</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>554</v>
+        <v>752</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>155</v>
+        <v>753</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="s">
-        <v>717</v>
+        <v>754</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>718</v>
+        <v>755</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>719</v>
+        <v>756</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
-        <v>720</v>
+        <v>757</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>721</v>
+        <v>758</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>722</v>
+        <v>735</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
-        <v>723</v>
+        <v>759</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>724</v>
+        <v>760</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>694</v>
+        <v>761</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>589</v>
+        <v>763</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>590</v>
+        <v>764</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="286" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="286" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="B286" s="3" t="s">
-        <v>727</v>
-      </c>
-      <c r="C286" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="D286" s="3"/>
-      <c r="E286" s="3"/>
+        <v>765</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>766</v>
+      </c>
       <c r="F286" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
-        <v>729</v>
+        <v>767</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>151</v>
+        <v>768</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>152</v>
+        <v>769</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
-        <v>730</v>
+        <v>770</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>731</v>
+        <v>771</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="289" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="289" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
-        <v>733</v>
-      </c>
-      <c r="B289" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="C289" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="D289" s="3"/>
-      <c r="E289" s="3"/>
+        <v>773</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>518</v>
+      </c>
       <c r="F289" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>736</v>
+        <v>774</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>151</v>
+        <v>775</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>152</v>
+        <v>776</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>737</v>
+        <v>777</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>738</v>
+        <v>778</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>739</v>
+        <v>779</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
-        <v>740</v>
+        <v>780</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>741</v>
+        <v>781</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>742</v>
+        <v>782</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="293" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="s">
-        <v>743</v>
-      </c>
-      <c r="B293" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="C293" s="1" t="s">
-        <v>745</v>
-      </c>
+        <v>783</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="C293" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="D293" s="3"/>
+      <c r="E293" s="3"/>
       <c r="F293" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="s">
-        <v>746</v>
+        <v>786</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>747</v>
+        <v>226</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>332</v>
+        <v>227</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="295" customFormat="false" ht="132.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="s">
-        <v>748</v>
+        <v>787</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>749</v>
+        <v>788</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>750</v>
+        <v>789</v>
       </c>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
       <c r="F295" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="s">
-        <v>751</v>
+        <v>790</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="1" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>731</v>
+        <v>629</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>732</v>
+        <v>230</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="298" customFormat="false" ht="280.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="B298" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="C298" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D298" s="3"/>
-      <c r="E298" s="3"/>
+        <v>792</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>794</v>
+      </c>
       <c r="F298" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="s">
-        <v>756</v>
+        <v>795</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>151</v>
+        <v>796</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>152</v>
+        <v>797</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="s">
-        <v>757</v>
+        <v>798</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>554</v>
+        <v>799</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>155</v>
+        <v>769</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="1" t="s">
-        <v>758</v>
+        <v>800</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>759</v>
+        <v>664</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>760</v>
+        <v>665</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="302" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="302" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="B302" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>375</v>
-      </c>
+        <v>801</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="C302" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="D302" s="3"/>
+      <c r="E302" s="3"/>
       <c r="F302" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="1" t="s">
-        <v>763</v>
+        <v>804</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>764</v>
+        <v>226</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>765</v>
+        <v>227</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="1" t="s">
-        <v>766</v>
+        <v>805</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>731</v>
+        <v>806</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>767</v>
+        <v>807</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="305" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="305" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="B305" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="C305" s="1" t="s">
-        <v>770</v>
-      </c>
+        <v>808</v>
+      </c>
+      <c r="B305" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="C305" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="D305" s="3"/>
+      <c r="E305" s="3"/>
       <c r="F305" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="1" t="s">
-        <v>771</v>
+        <v>811</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>772</v>
+        <v>226</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>773</v>
+        <v>227</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="1" t="s">
-        <v>774</v>
+        <v>812</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>775</v>
+        <v>813</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>369</v>
+        <v>814</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="308" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="308" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="1" t="s">
-        <v>776</v>
+        <v>815</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="C308" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="D308" s="3"/>
-      <c r="E308" s="3"/>
+        <v>816</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>817</v>
+      </c>
       <c r="F308" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="1" t="s">
-        <v>779</v>
+        <v>818</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>151</v>
+        <v>819</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>152</v>
+        <v>820</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="310" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="310" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="B310" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="C310" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="D310" s="3"/>
-      <c r="E310" s="3"/>
+        <v>821</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>407</v>
+      </c>
       <c r="F310" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="311" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="311" customFormat="false" ht="132.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="B311" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>152</v>
-      </c>
+        <v>823</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="C311" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="D311" s="3"/>
+      <c r="E311" s="3"/>
       <c r="F311" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>784</v>
+        <v>826</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>785</v>
+        <v>226</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>786</v>
+        <v>227</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>787</v>
+        <v>827</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>785</v>
+        <v>806</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>786</v>
+        <v>807</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="314" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="314" customFormat="false" ht="280.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="B314" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C314" s="1" t="s">
-        <v>246</v>
-      </c>
+        <v>828</v>
+      </c>
+      <c r="B314" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="C314" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="D314" s="3"/>
+      <c r="E314" s="3"/>
       <c r="F314" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
-        <v>789</v>
+        <v>831</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>790</v>
+        <v>226</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>790</v>
+        <v>227</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
-        <v>791</v>
+        <v>832</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>792</v>
+        <v>629</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>793</v>
+        <v>230</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>794</v>
+        <v>833</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>795</v>
+        <v>834</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>796</v>
+        <v>835</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
-        <v>797</v>
+        <v>836</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>795</v>
+        <v>837</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>798</v>
+        <v>450</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
-        <v>799</v>
+        <v>838</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>800</v>
+        <v>839</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>801</v>
+        <v>840</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
-        <v>802</v>
+        <v>841</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>804</v>
+        <v>842</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="s">
-        <v>805</v>
+        <v>843</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>287</v>
+        <v>844</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>288</v>
+        <v>845</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="1" t="s">
-        <v>806</v>
+        <v>846</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>195</v>
+        <v>847</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>196</v>
+        <v>848</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
-        <v>807</v>
+        <v>849</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>192</v>
+        <v>850</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>193</v>
+        <v>444</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="324" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="324" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
-        <v>808</v>
+        <v>851</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="C324" s="1" t="s">
-        <v>810</v>
-      </c>
+        <v>852</v>
+      </c>
+      <c r="C324" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="D324" s="3"/>
+      <c r="E324" s="3"/>
       <c r="F324" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
-        <v>811</v>
+        <v>854</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>479</v>
+        <v>226</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>812</v>
+        <v>227</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A326" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="B326" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="C326" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="D326" s="3"/>
+      <c r="E326" s="3"/>
+      <c r="F326" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G326" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A327" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F327" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G327" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A328" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="F328" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G328" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A329" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="F329" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G329" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="330" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A330" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="F330" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G330" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A331" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="F331" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G331" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="F332" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G332" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="F333" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G333" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="334" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A334" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="F334" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G334" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="335" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A335" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="F335" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G335" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A336" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F336" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G336" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A337" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F337" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G337" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="338" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A338" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F338" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G338" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="339" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A339" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F339" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G339" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="340" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A340" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="F340" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G340" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="341" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A341" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="F341" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G341" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1048513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
